--- a/resources/templates/M2_Morbidity.xlsx
+++ b/resources/templates/M2_Morbidity.xlsx
@@ -2503,18 +2503,18 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -2542,12 +2542,12 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>2219325</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="180975" cy="190500"/>
+    <xdr:ext cx="1466850" cy="1544052"/>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="2" name="image1.png"/>
@@ -2560,6 +2560,10 @@
         </a:stretch>
       </xdr:blipFill>
       <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2219325" y="0"/>
+          <a:ext cx="1466850" cy="1544052"/>
+        </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
@@ -2571,11 +2575,11 @@
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:colOff>352424</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>171450</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="190500" cy="190500"/>
+    <xdr:ext cx="1247775" cy="1143000"/>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="3" name="image2.png"/>
@@ -2588,6 +2592,10 @@
         </a:stretch>
       </xdr:blipFill>
       <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3714749" y="171450"/>
+          <a:ext cx="1247775" cy="1143000"/>
+        </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
@@ -2871,20 +2879,20 @@
     </row>
     <row r="2" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A2" s="5"/>
-      <c r="B2" s="36"/>
+      <c r="B2" s="37"/>
       <c r="C2" s="43"/>
-      <c r="D2" s="36"/>
-      <c r="E2" s="36"/>
-      <c r="F2" s="36"/>
+      <c r="D2" s="37"/>
+      <c r="E2" s="37"/>
+      <c r="F2" s="37"/>
       <c r="G2" s="1"/>
       <c r="H2" s="6"/>
-      <c r="I2" s="39" t="s">
+      <c r="I2" s="36" t="s">
         <v>1</v>
       </c>
-      <c r="J2" s="36"/>
-      <c r="K2" s="36"/>
-      <c r="L2" s="36"/>
-      <c r="M2" s="36"/>
+      <c r="J2" s="37"/>
+      <c r="K2" s="37"/>
+      <c r="L2" s="37"/>
+      <c r="M2" s="37"/>
       <c r="N2" s="7"/>
       <c r="O2" s="7" t="s">
         <v>2</v>
@@ -2925,27 +2933,27 @@
       <c r="AW2" s="44" t="s">
         <v>3</v>
       </c>
-      <c r="AX2" s="36"/>
-      <c r="AY2" s="36"/>
-      <c r="AZ2" s="36"/>
+      <c r="AX2" s="37"/>
+      <c r="AY2" s="37"/>
+      <c r="AZ2" s="37"/>
       <c r="BA2" s="4"/>
     </row>
     <row r="3" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A3" s="5"/>
-      <c r="B3" s="36"/>
-      <c r="C3" s="36"/>
-      <c r="D3" s="36"/>
-      <c r="E3" s="36"/>
-      <c r="F3" s="36"/>
+      <c r="B3" s="37"/>
+      <c r="C3" s="37"/>
+      <c r="D3" s="37"/>
+      <c r="E3" s="37"/>
+      <c r="F3" s="37"/>
       <c r="G3" s="1"/>
       <c r="H3" s="6"/>
-      <c r="I3" s="39" t="s">
+      <c r="I3" s="36" t="s">
         <v>4</v>
       </c>
-      <c r="J3" s="36"/>
-      <c r="K3" s="36"/>
-      <c r="L3" s="36"/>
-      <c r="M3" s="36"/>
+      <c r="J3" s="37"/>
+      <c r="K3" s="37"/>
+      <c r="L3" s="37"/>
+      <c r="M3" s="37"/>
       <c r="N3" s="7"/>
       <c r="O3" s="7" t="s">
         <v>5</v>
@@ -2983,28 +2991,28 @@
       <c r="AT3" s="4"/>
       <c r="AU3" s="4"/>
       <c r="AV3" s="4"/>
-      <c r="AW3" s="36"/>
-      <c r="AX3" s="36"/>
-      <c r="AY3" s="36"/>
-      <c r="AZ3" s="36"/>
+      <c r="AW3" s="37"/>
+      <c r="AX3" s="37"/>
+      <c r="AY3" s="37"/>
+      <c r="AZ3" s="37"/>
       <c r="BA3" s="4"/>
     </row>
     <row r="4" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A4" s="5"/>
-      <c r="B4" s="36"/>
-      <c r="C4" s="36"/>
-      <c r="D4" s="36"/>
-      <c r="E4" s="36"/>
-      <c r="F4" s="36"/>
+      <c r="B4" s="37"/>
+      <c r="C4" s="37"/>
+      <c r="D4" s="37"/>
+      <c r="E4" s="37"/>
+      <c r="F4" s="37"/>
       <c r="G4" s="1"/>
       <c r="H4" s="6"/>
-      <c r="I4" s="39" t="s">
+      <c r="I4" s="36" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="36"/>
-      <c r="K4" s="36"/>
-      <c r="L4" s="36"/>
-      <c r="M4" s="36"/>
+      <c r="J4" s="37"/>
+      <c r="K4" s="37"/>
+      <c r="L4" s="37"/>
+      <c r="M4" s="37"/>
       <c r="N4" s="7"/>
       <c r="O4" s="7" t="s">
         <v>5</v>
@@ -3042,28 +3050,28 @@
       <c r="AT4" s="4"/>
       <c r="AU4" s="4"/>
       <c r="AV4" s="4"/>
-      <c r="AW4" s="36"/>
-      <c r="AX4" s="36"/>
-      <c r="AY4" s="36"/>
-      <c r="AZ4" s="36"/>
+      <c r="AW4" s="37"/>
+      <c r="AX4" s="37"/>
+      <c r="AY4" s="37"/>
+      <c r="AZ4" s="37"/>
       <c r="BA4" s="4"/>
     </row>
     <row r="5" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A5" s="5"/>
-      <c r="B5" s="36"/>
-      <c r="C5" s="36"/>
-      <c r="D5" s="36"/>
-      <c r="E5" s="36"/>
-      <c r="F5" s="36"/>
+      <c r="B5" s="37"/>
+      <c r="C5" s="37"/>
+      <c r="D5" s="37"/>
+      <c r="E5" s="37"/>
+      <c r="F5" s="37"/>
       <c r="G5" s="1"/>
       <c r="H5" s="6"/>
-      <c r="I5" s="39" t="s">
+      <c r="I5" s="36" t="s">
         <v>7</v>
       </c>
-      <c r="J5" s="36"/>
-      <c r="K5" s="36"/>
-      <c r="L5" s="36"/>
-      <c r="M5" s="36"/>
+      <c r="J5" s="37"/>
+      <c r="K5" s="37"/>
+      <c r="L5" s="37"/>
+      <c r="M5" s="37"/>
       <c r="N5" s="7"/>
       <c r="O5" s="7" t="s">
         <v>5</v>
@@ -3101,28 +3109,28 @@
       <c r="AT5" s="4"/>
       <c r="AU5" s="4"/>
       <c r="AV5" s="4"/>
-      <c r="AW5" s="36"/>
-      <c r="AX5" s="36"/>
-      <c r="AY5" s="36"/>
-      <c r="AZ5" s="36"/>
+      <c r="AW5" s="37"/>
+      <c r="AX5" s="37"/>
+      <c r="AY5" s="37"/>
+      <c r="AZ5" s="37"/>
       <c r="BA5" s="4"/>
     </row>
     <row r="6" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A6" s="5"/>
-      <c r="B6" s="36"/>
-      <c r="C6" s="36"/>
-      <c r="D6" s="36"/>
-      <c r="E6" s="36"/>
-      <c r="F6" s="36"/>
+      <c r="B6" s="37"/>
+      <c r="C6" s="37"/>
+      <c r="D6" s="37"/>
+      <c r="E6" s="37"/>
+      <c r="F6" s="37"/>
       <c r="G6" s="1"/>
       <c r="H6" s="6"/>
-      <c r="I6" s="39" t="s">
+      <c r="I6" s="36" t="s">
         <v>8</v>
       </c>
-      <c r="J6" s="36"/>
-      <c r="K6" s="36"/>
-      <c r="L6" s="36"/>
-      <c r="M6" s="36"/>
+      <c r="J6" s="37"/>
+      <c r="K6" s="37"/>
+      <c r="L6" s="37"/>
+      <c r="M6" s="37"/>
       <c r="N6" s="7"/>
       <c r="O6" s="7" t="s">
         <v>5</v>
@@ -3160,28 +3168,28 @@
       <c r="AT6" s="4"/>
       <c r="AU6" s="4"/>
       <c r="AV6" s="4"/>
-      <c r="AW6" s="36"/>
-      <c r="AX6" s="36"/>
-      <c r="AY6" s="36"/>
-      <c r="AZ6" s="36"/>
+      <c r="AW6" s="37"/>
+      <c r="AX6" s="37"/>
+      <c r="AY6" s="37"/>
+      <c r="AZ6" s="37"/>
       <c r="BA6" s="4"/>
     </row>
     <row r="7" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A7" s="5"/>
-      <c r="B7" s="36"/>
-      <c r="C7" s="36"/>
-      <c r="D7" s="36"/>
-      <c r="E7" s="36"/>
-      <c r="F7" s="36"/>
+      <c r="B7" s="37"/>
+      <c r="C7" s="37"/>
+      <c r="D7" s="37"/>
+      <c r="E7" s="37"/>
+      <c r="F7" s="37"/>
       <c r="G7" s="1"/>
       <c r="H7" s="6"/>
-      <c r="I7" s="39" t="s">
+      <c r="I7" s="36" t="s">
         <v>9</v>
       </c>
-      <c r="J7" s="36"/>
-      <c r="K7" s="36"/>
-      <c r="L7" s="36"/>
-      <c r="M7" s="36"/>
+      <c r="J7" s="37"/>
+      <c r="K7" s="37"/>
+      <c r="L7" s="37"/>
+      <c r="M7" s="37"/>
       <c r="N7" s="7"/>
       <c r="O7" s="7" t="s">
         <v>5</v>
@@ -3219,15 +3227,15 @@
       <c r="AT7" s="4"/>
       <c r="AU7" s="4"/>
       <c r="AV7" s="4"/>
-      <c r="AW7" s="36"/>
-      <c r="AX7" s="36"/>
-      <c r="AY7" s="36"/>
-      <c r="AZ7" s="36"/>
+      <c r="AW7" s="37"/>
+      <c r="AX7" s="37"/>
+      <c r="AY7" s="37"/>
+      <c r="AZ7" s="37"/>
       <c r="BA7" s="4"/>
     </row>
     <row r="8" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A8" s="5"/>
-      <c r="B8" s="36"/>
+      <c r="B8" s="37"/>
       <c r="C8" s="1"/>
       <c r="D8" s="1"/>
       <c r="E8" s="1"/>
@@ -3238,18 +3246,18 @@
       <c r="J8" s="1"/>
       <c r="K8" s="12"/>
       <c r="L8" s="12"/>
-      <c r="M8" s="40" t="s">
+      <c r="M8" s="38" t="s">
         <v>10</v>
       </c>
-      <c r="N8" s="36"/>
-      <c r="O8" s="36"/>
-      <c r="P8" s="36"/>
-      <c r="Q8" s="36"/>
-      <c r="R8" s="36"/>
-      <c r="S8" s="36"/>
-      <c r="T8" s="36"/>
-      <c r="U8" s="36"/>
-      <c r="V8" s="36"/>
+      <c r="N8" s="37"/>
+      <c r="O8" s="37"/>
+      <c r="P8" s="37"/>
+      <c r="Q8" s="37"/>
+      <c r="R8" s="37"/>
+      <c r="S8" s="37"/>
+      <c r="T8" s="37"/>
+      <c r="U8" s="37"/>
+      <c r="V8" s="37"/>
       <c r="W8" s="4"/>
       <c r="X8" s="4"/>
       <c r="Y8" s="4"/>
@@ -3283,61 +3291,61 @@
       <c r="BA8" s="4"/>
     </row>
     <row r="9" spans="1:53" x14ac:dyDescent="0.2">
-      <c r="A9" s="41" t="s">
+      <c r="A9" s="39" t="s">
         <v>11</v>
       </c>
-      <c r="B9" s="37"/>
-      <c r="C9" s="37"/>
-      <c r="D9" s="37"/>
-      <c r="E9" s="37"/>
-      <c r="F9" s="37"/>
-      <c r="G9" s="37"/>
-      <c r="H9" s="37"/>
-      <c r="I9" s="37"/>
-      <c r="J9" s="37"/>
-      <c r="K9" s="37"/>
-      <c r="L9" s="37"/>
-      <c r="M9" s="37"/>
-      <c r="N9" s="37"/>
-      <c r="O9" s="37"/>
-      <c r="P9" s="37"/>
-      <c r="Q9" s="37"/>
-      <c r="R9" s="37"/>
-      <c r="S9" s="37"/>
-      <c r="T9" s="37"/>
-      <c r="U9" s="37"/>
-      <c r="V9" s="37"/>
-      <c r="W9" s="37"/>
-      <c r="X9" s="37"/>
-      <c r="Y9" s="37"/>
-      <c r="Z9" s="37"/>
-      <c r="AA9" s="37"/>
-      <c r="AB9" s="37"/>
-      <c r="AC9" s="37"/>
-      <c r="AD9" s="37"/>
-      <c r="AE9" s="37"/>
-      <c r="AF9" s="37"/>
-      <c r="AG9" s="37"/>
-      <c r="AH9" s="37"/>
-      <c r="AI9" s="37"/>
-      <c r="AJ9" s="37"/>
-      <c r="AK9" s="37"/>
-      <c r="AL9" s="37"/>
-      <c r="AM9" s="37"/>
-      <c r="AN9" s="37"/>
-      <c r="AO9" s="37"/>
-      <c r="AP9" s="37"/>
-      <c r="AQ9" s="37"/>
-      <c r="AR9" s="37"/>
-      <c r="AS9" s="37"/>
-      <c r="AT9" s="37"/>
-      <c r="AU9" s="37"/>
-      <c r="AV9" s="37"/>
-      <c r="AW9" s="37"/>
-      <c r="AX9" s="37"/>
-      <c r="AY9" s="37"/>
-      <c r="AZ9" s="37"/>
-      <c r="BA9" s="38"/>
+      <c r="B9" s="40"/>
+      <c r="C9" s="40"/>
+      <c r="D9" s="40"/>
+      <c r="E9" s="40"/>
+      <c r="F9" s="40"/>
+      <c r="G9" s="40"/>
+      <c r="H9" s="40"/>
+      <c r="I9" s="40"/>
+      <c r="J9" s="40"/>
+      <c r="K9" s="40"/>
+      <c r="L9" s="40"/>
+      <c r="M9" s="40"/>
+      <c r="N9" s="40"/>
+      <c r="O9" s="40"/>
+      <c r="P9" s="40"/>
+      <c r="Q9" s="40"/>
+      <c r="R9" s="40"/>
+      <c r="S9" s="40"/>
+      <c r="T9" s="40"/>
+      <c r="U9" s="40"/>
+      <c r="V9" s="40"/>
+      <c r="W9" s="40"/>
+      <c r="X9" s="40"/>
+      <c r="Y9" s="40"/>
+      <c r="Z9" s="40"/>
+      <c r="AA9" s="40"/>
+      <c r="AB9" s="40"/>
+      <c r="AC9" s="40"/>
+      <c r="AD9" s="40"/>
+      <c r="AE9" s="40"/>
+      <c r="AF9" s="40"/>
+      <c r="AG9" s="40"/>
+      <c r="AH9" s="40"/>
+      <c r="AI9" s="40"/>
+      <c r="AJ9" s="40"/>
+      <c r="AK9" s="40"/>
+      <c r="AL9" s="40"/>
+      <c r="AM9" s="40"/>
+      <c r="AN9" s="40"/>
+      <c r="AO9" s="40"/>
+      <c r="AP9" s="40"/>
+      <c r="AQ9" s="40"/>
+      <c r="AR9" s="40"/>
+      <c r="AS9" s="40"/>
+      <c r="AT9" s="40"/>
+      <c r="AU9" s="40"/>
+      <c r="AV9" s="40"/>
+      <c r="AW9" s="40"/>
+      <c r="AX9" s="40"/>
+      <c r="AY9" s="40"/>
+      <c r="AZ9" s="40"/>
+      <c r="BA9" s="41"/>
     </row>
     <row r="10" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A10" s="13" t="s">
